--- a/BaoCao/localization.xlsx
+++ b/BaoCao/localization.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Localization_testing\BaoCao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0220C11-174A-4298-83F5-E910B6C82F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4E8023-5FF3-4BCF-AB8E-0077401E3CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{B8891744-BF1A-4F43-AF5F-827B9606D4E5}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="424">
   <si>
     <t>Hạng mục</t>
   </si>
@@ -276,15 +276,6 @@
     <t>B. KỸ THUẬT PHÂN TÍCH GIÁ TRỊ BIÊN</t>
   </si>
   <si>
-    <t>Mã Biên (Boundary ID)</t>
-  </si>
-  <si>
-    <t>50 ký tự</t>
-  </si>
-  <si>
-    <t>80 ký tự</t>
-  </si>
-  <si>
     <t>Tiếng Việt (vi)</t>
   </si>
   <si>
@@ -333,36 +324,6 @@
     <t>• Yêu cầu lật ngược layout giao diện.</t>
   </si>
   <si>
-    <t>Loại kiểm tra</t>
-  </si>
-  <si>
-    <t>Giá trị Biên (Threshold)</t>
-  </si>
-  <si>
-    <t>Mục tiêu kiểm thử</t>
-  </si>
-  <si>
-    <t>Tràn Khung (Overflow)</t>
-  </si>
-  <si>
-    <t>Tỷ lệ 1:1</t>
-  </si>
-  <si>
-    <t>Kiểm tra nội dung có tràn ra khỏi khung chứa (Button/Menu) không.</t>
-  </si>
-  <si>
-    <t>Cảnh báo độ dài</t>
-  </si>
-  <si>
-    <t>Cảnh báo các Tiêu đề (Heading) quá dài.</t>
-  </si>
-  <si>
-    <t>Lỗi độ dài (Error)</t>
-  </si>
-  <si>
-    <t>Báo lỗi các Nút bấm (Button) có text dài &gt; 80 ký tự (Gây vỡ layout Mobile).</t>
-  </si>
-  <si>
     <t>C. DANH SÁCH TEST CASE ĐỀ XUẤT</t>
   </si>
   <si>
@@ -381,9 +342,6 @@
     <t>Kết quả mong đợi (Expected Result)</t>
   </si>
   <si>
-    <t>Kết quả thực tế (Actual)</t>
-  </si>
-  <si>
     <t>TC_LOC_01</t>
   </si>
   <si>
@@ -1476,9 +1434,6 @@
     <t>5. Charset (Font &amp; Encoding)</t>
   </si>
   <si>
-    <t>6. Func (Chức năng cơ bản)</t>
-  </si>
-  <si>
     <t>Test Suite:</t>
   </si>
   <si>
@@ -1647,15 +1602,9 @@
     <t>1 sec 584 ms</t>
   </si>
   <si>
-    <t>Tìm thấy 2 từ tiếng Anh chưa dịch (tối đa cho phép: 1)</t>
-  </si>
-  <si>
     <t>1 sec 588 ms</t>
   </si>
   <si>
-    <t>Tìm thấy 3 từ tiếng Anh chưa dịch (tối đa cho phép: 1)</t>
-  </si>
-  <si>
     <t>TEST 06: Character Encoding</t>
   </si>
   <si>
@@ -1674,22 +1623,13 @@
     <t>BUG-LOC-001</t>
   </si>
   <si>
-    <t>TC-AUTO-01-EN</t>
-  </si>
-  <si>
     <t>Currency Format</t>
   </si>
   <si>
     <t>BUG-LOC-002</t>
   </si>
   <si>
-    <t>TC-AUTO-01-VI</t>
-  </si>
-  <si>
     <t>BUG-LOC-003</t>
-  </si>
-  <si>
-    <t>TC-AUTO-01-AR</t>
   </si>
   <si>
     <t>Currency symbol incorrect: found '€' instead of 'ر.س'</t>
@@ -1706,24 +1646,12 @@
     <t>BUG-LOC-004</t>
   </si>
   <si>
-    <t>TC-AUTO-03-AR</t>
-  </si>
-  <si>
     <t>BUG-LOC-005</t>
   </si>
   <si>
-    <t>TC-AUTO-05-VI</t>
-  </si>
-  <si>
-    <t>Translation Coverage</t>
-  </si>
-  <si>
     <t>BUG-LOC-006</t>
   </si>
   <si>
-    <t>TC-AUTO-05-AR</t>
-  </si>
-  <si>
     <t>Số Case IGNORED</t>
   </si>
   <si>
@@ -1798,9 +1726,6 @@
     <t>Bố cục LTR đúng</t>
   </si>
   <si>
-    <t>Bản dịch chấp nhận được cho bản demo</t>
-  </si>
-  <si>
     <t>Các danh mục chính chưa được dịch</t>
   </si>
   <si>
@@ -1844,15 +1769,6 @@
   </si>
   <si>
     <t>Tối đa 1 từ chưa dịch, độ bao phủ ≥ 20%</t>
-  </si>
-  <si>
-    <t>0 từ chưa dịch, độ bao phủ 30%</t>
-  </si>
-  <si>
-    <t>2 từ chưa dịch: About us, Terms and conditions. Độ bao phủ: 30%</t>
-  </si>
-  <si>
-    <t>3 từ chưa dịch: About us, Clothes, Accessories. Độ bao phủ: 20%</t>
   </si>
   <si>
     <t>Footer chưa được dịch</t>
@@ -1988,14 +1904,6 @@
 4. Xác thực ký hiệu và định dạng</t>
   </si>
   <si>
-    <t>Giá hiển thị:
-• 22.94 €
-• 34.46 €
-• 34.80 €
-• 14.28 €
-Định dạng thập phân đúng nhưng ký hiệu sai.</t>
-  </si>
-  <si>
     <t>Không đặt hướng RTL cho ngôn ngữ Arabic</t>
   </si>
   <si>
@@ -2024,12 +1932,6 @@
 Toàn bộ UI vẫn LTR → sai hoàn toàn với Arabic.</t>
   </si>
   <si>
-    <t>Văn bản tiếng Anh chưa dịch: About us, Terms and conditions</t>
-  </si>
-  <si>
-    <t>Test phát hiện 2 cụm tiếng Anh chưa dịch trong phiên bản Tiếng Việt. Độ phủ keyword chỉ 30%.</t>
-  </si>
-  <si>
     <t>• Ngôn ngữ Tiếng Việt đang active
 • Quét toàn bộ text trang</t>
   </si>
@@ -2038,24 +1940,6 @@
 2. Lấy toàn bộ text body
 3. Quét danh sách từ tiếng Anh cấm
 4. Kiểm tra keyword Tiếng Việt mong đợi</t>
-  </si>
-  <si>
-    <t>Không có text tiếng Anh
-'About us' → 'Về chúng tôi'
-'Terms and conditions' → 'Điều khoản và điều kiện'
-Độ phủ keyword ≥ 50%</t>
-  </si>
-  <si>
-    <t>Tìm thấy tiếng Anh:
-• 'About us' (footer)
-• 'Terms and conditions' (footer)
-Độ phủ keyword Việt: 30% (chỉ tìm thấy Đăng nhập, Liên hệ, Giỏ hàng)</t>
-  </si>
-  <si>
-    <t>Văn bản tiếng Anh chưa dịch: About us, Clothes, Accessories</t>
-  </si>
-  <si>
-    <t>Test Arabic phát hiện 3 cụm tiếng Anh chưa dịch. Độ phủ keyword chỉ 20%.</t>
   </si>
   <si>
     <t>• Ngôn ngữ Arabic (ar)
@@ -2067,19 +1951,6 @@
 3. Kiểm tra danh sách 18 từ cấm
 4. Kiểm tra 10 keyword Arabic mong đợi
 5. Tính % độ phủ</t>
-  </si>
-  <si>
-    <t>Không có từ tiếng Anh
-'Clothes' → 'ملابس'
-'Accessories' → 'إكسسوارات'
-Độ phủ keyword ≥ 50%</t>
-  </si>
-  <si>
-    <t>Tìm thấy 3 cụm chưa dịch:
-• 'About us' (footer)
-• 'Clothes' (menu danh mục)
-• 'Accessories' (menu danh mục)
-Độ phủ Arabic: 20% (chỉ 2/10)</t>
   </si>
   <si>
     <t>Bản dịch Arabic rất thiếu. Danh mục chính và các thuật ngữ mua sắm chưa dịch.</t>
@@ -2143,6 +2014,214 @@
 2. Thêm USD
 3. Đặt USD làm mặc định cho English
 HOẶC cập nhật kỳ vọng test chấp nhận € trên demo</t>
+  </si>
+  <si>
+    <t>Mã Biên (BVA ID)</t>
+  </si>
+  <si>
+    <t>Loại Giá Trị Biên</t>
+  </si>
+  <si>
+    <t>Quy tắc xác định (Công thức tính toán)</t>
+  </si>
+  <si>
+    <t>Dữ liệu test (Text Length)</t>
+  </si>
+  <si>
+    <t>Giá trị bình thường (Nominal)</t>
+  </si>
+  <si>
+    <t>Text Width &lt; Container Width (Ký tự ngắn)</t>
+  </si>
+  <si>
+    <t>10 - 20 ký tự (VD: Add to cart)</t>
+  </si>
+  <si>
+    <t>Giá trị Cận biên (Max)</t>
+  </si>
+  <si>
+    <t>Text Width = Container Width (Vừa khít khung)</t>
+  </si>
+  <si>
+    <t>~30 ký tự (VD: Ajouter au panier)</t>
+  </si>
+  <si>
+    <t>Giá trị Vượt biên (Max + 1)</t>
+  </si>
+  <si>
+    <t>Text Width &gt; Container Width (Dài hơn khung)</t>
+  </si>
+  <si>
+    <t>&gt; 40 ký tự (VD: Thêm sản phẩm này vào giỏ hàng của bạn)</t>
+  </si>
+  <si>
+    <t>Điều kiện (Conditions)</t>
+  </si>
+  <si>
+    <t>Điều kiện đầu vào (Conditions)</t>
+  </si>
+  <si>
+    <t>Rule 1</t>
+  </si>
+  <si>
+    <t>Rule 2</t>
+  </si>
+  <si>
+    <t>Rule 3</t>
+  </si>
+  <si>
+    <t>Rule 4</t>
+  </si>
+  <si>
+    <t>C1: Ngôn ngữ được chọn là tiếng Anh (en-US)</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>C2: Ngôn ngữ được chọn là tiếng Pháp (fr-FR)</t>
+  </si>
+  <si>
+    <t>C3: Ngôn ngữ được chọn là tiếng Việt (vi-VN)</t>
+  </si>
+  <si>
+    <t>C4: Ngôn ngữ được chọn là tiếng Ả Rập (ar-SA)</t>
+  </si>
+  <si>
+    <t>Hành động (Actions)</t>
+  </si>
+  <si>
+    <t>Hành động mong đợi (Actions)</t>
+  </si>
+  <si>
+    <t>A1: Định dạng tiền tệ: Prefix $, Decimal (.)</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>A2: Định dạng tiền tệ: Suffix €, Decimal (,)</t>
+  </si>
+  <si>
+    <t>A3: Định dạng tiền tệ: Suffix ₫, Decimal (,)</t>
+  </si>
+  <si>
+    <t>A4: Định dạng tiền tệ: Suffix ر.س, Decimal (.)</t>
+  </si>
+  <si>
+    <t>A5: Cập nhật thẻ HTML: &lt;html dir="ltr"&gt;</t>
+  </si>
+  <si>
+    <t>A6: Cập nhật thẻ HTML: &lt;html dir="rtl"&gt;</t>
+  </si>
+  <si>
+    <t>A7: Căn lề UI (Layout Alignment): Trái (Left)</t>
+  </si>
+  <si>
+    <t>A8: Căn lề UI (Layout Alignment): Phải (Right)</t>
+  </si>
+  <si>
+    <t>6. Charset (Mã hóa ký tự)</t>
+  </si>
+  <si>
+    <t>TC-Currency-EN</t>
+  </si>
+  <si>
+    <t>TC-Currency-VI</t>
+  </si>
+  <si>
+    <t>TC-Currency-AR</t>
+  </si>
+  <si>
+    <t>TC-Layout_Direction-AR</t>
+  </si>
+  <si>
+    <t>TC-Untranslated_Text-VI</t>
+  </si>
+  <si>
+    <t>TC-Untranslated_Text-AR</t>
+  </si>
+  <si>
+    <t>1 từ chưa dịch</t>
+  </si>
+  <si>
+    <t>7 từ chưa dịch</t>
+  </si>
+  <si>
+    <t>8 từ chưa dịch</t>
+  </si>
+  <si>
+    <t>Tìm thấy 1 từ tiếng Anh chưa dịch (tối đa cho phép: 1)</t>
+  </si>
+  <si>
+    <t>Tìm thấy 7 từ tiếng Anh chưa dịch (tối đa cho phép: 1)</t>
+  </si>
+  <si>
+    <t>Tìm thấy 8 từ tiếng Anh chưa dịch (tối đa cho phép: 1)</t>
+  </si>
+  <si>
+    <t>Giá hiển thị:
+• 22.94 ر.س
+• 34.46 ر.س
+• 34.80 ر.س
+• 14.28 ر.س
+Định dạng thập phân đúng nhưng ký hiệu sai.</t>
+  </si>
+  <si>
+    <t>TC-Untranslated_Text-FR</t>
+  </si>
+  <si>
+    <t>Untranslated Text</t>
+  </si>
+  <si>
+    <t>Sót 1 từ khóa tiếng Anh chưa dịch trên giao diện</t>
+  </si>
+  <si>
+    <t>Sót 7 từ khóa tiếng Anh chưa dịch trên giao diện</t>
+  </si>
+  <si>
+    <t>Sót 8 từ khóa tiếng Anh chưa dịch trên giao diện</t>
+  </si>
+  <si>
+    <t>Thanh tìm kiếm vẫn hiển thị Placeholder tiếng Anh.</t>
+  </si>
+  <si>
+    <t>Footer và Menu chưa được dịch sang tiếng Việt.</t>
+  </si>
+  <si>
+    <t>Footer và Menu chưa được dịch sang tiếng Ả Rập.</t>
+  </si>
+  <si>
+    <t>1. Chuyển sang Pháp
+2. Quét tìm từ tiếng Anh
+3. Kiểm tra danh sách 18 từ cấm
+4. Kiểm tra 10 keyword Arabic mong đợi
+5. Tính % độ phủ</t>
+  </si>
+  <si>
+    <t>• Ngôn ngữ Français (fr)
+• Quét text trang</t>
+  </si>
+  <si>
+    <t>Phát hiện 1 từ chưa dịch: "Search".</t>
+  </si>
+  <si>
+    <t>Không còn từ khóa tiếng Anh nào trên giao diện.</t>
+  </si>
+  <si>
+    <t>Phát hiện 7 từ chưa dịch: "About us", "Secure payment", "Terms and Conditions", "Clothes", "Accessories", "Search".</t>
+  </si>
+  <si>
+    <t>Phát hiện 8 từ chưa dịch: "About us", "Legal Notice", "Secure payment", "Terms and Conditions", "Clothes", "Accessories", "Search", "Delivery".</t>
+  </si>
+  <si>
+    <t>1. Dịch 'Search' =&gt; "Recherche'</t>
+  </si>
+  <si>
+    <t>BUG-LOC-007</t>
   </si>
 </sst>
 </file>
@@ -2152,7 +2231,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2212,8 +2291,49 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2274,8 +2394,20 @@
         <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -2548,18 +2680,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF9E9E9E"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF9E9E9E"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF9E9E9E"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF9E9E9E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF9E9E9E"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
@@ -2626,184 +2780,204 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3118,360 +3292,360 @@
   <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="39.7265625" style="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.81640625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="46.7265625" style="20" customWidth="1"/>
-    <col min="4" max="16384" width="8.7265625" style="20"/>
+    <col min="1" max="1" width="39.7265625" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.81640625" style="19" customWidth="1"/>
+    <col min="3" max="3" width="46.7265625" style="19" customWidth="1"/>
+    <col min="4" max="16384" width="8.7265625" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="53" t="s">
-        <v>214</v>
+      <c r="B3" s="33" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="33" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="33" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="33" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="53" t="s">
-        <v>349</v>
+      <c r="B7" s="33" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="91">
+      <c r="B8" s="56">
         <v>46055</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="42"/>
-      <c r="B9" s="42"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
     </row>
     <row r="11" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="33" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="63" t="s">
-        <v>215</v>
-      </c>
-      <c r="C14" s="54" t="s">
+      <c r="B14" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" s="79" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="26"/>
-      <c r="C15" s="55"/>
+      <c r="A15" s="78"/>
+      <c r="C15" s="80"/>
     </row>
     <row r="16" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26"/>
-      <c r="B16" s="63" t="s">
-        <v>216</v>
-      </c>
-      <c r="C16" s="55"/>
+      <c r="A16" s="78"/>
+      <c r="B16" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="C16" s="80"/>
     </row>
     <row r="17" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="26"/>
-      <c r="C17" s="55"/>
+      <c r="A17" s="78"/>
+      <c r="C17" s="80"/>
     </row>
     <row r="18" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="26"/>
-      <c r="B18" s="63" t="s">
-        <v>217</v>
-      </c>
-      <c r="C18" s="55"/>
+      <c r="A18" s="78"/>
+      <c r="B18" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="80"/>
     </row>
     <row r="19" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="26"/>
-      <c r="C19" s="55"/>
+      <c r="A19" s="78"/>
+      <c r="C19" s="80"/>
     </row>
     <row r="20" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="26"/>
-      <c r="B20" s="63" t="s">
-        <v>218</v>
-      </c>
-      <c r="C20" s="55"/>
+      <c r="A20" s="78"/>
+      <c r="B20" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" s="80"/>
     </row>
     <row r="21" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="26"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="55"/>
+      <c r="A21" s="78"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="80"/>
     </row>
     <row r="22" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="26"/>
-      <c r="B22" s="63" t="s">
-        <v>219</v>
-      </c>
-      <c r="C22" s="55"/>
+      <c r="A22" s="78"/>
+      <c r="B22" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" s="80"/>
     </row>
     <row r="23" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="26"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="55"/>
+      <c r="A23" s="78"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="80"/>
     </row>
     <row r="24" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="26"/>
-      <c r="B24" s="64" t="s">
-        <v>220</v>
-      </c>
-      <c r="C24" s="55"/>
+      <c r="A24" s="78"/>
+      <c r="B24" s="39" t="s">
+        <v>394</v>
+      </c>
+      <c r="C24" s="80"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="44" t="s">
+      <c r="B25" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="56" t="s">
+      <c r="C25" s="84" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="45"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="57"/>
+      <c r="A26" s="82"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="85"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="45"/>
-      <c r="B27" s="15" t="s">
+      <c r="A27" s="82"/>
+      <c r="B27" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="57"/>
+      <c r="C27" s="85"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="45"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="57"/>
+      <c r="A28" s="82"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="85"/>
     </row>
     <row r="29" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="46"/>
-      <c r="B29" s="47" t="s">
+      <c r="A29" s="83"/>
+      <c r="B29" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="58"/>
+      <c r="C29" s="86"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="42"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="42"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
     </row>
     <row r="32" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="65">
+      <c r="B34" s="28">
         <f>COUNTA('Test case'!B7:B500)</f>
         <v>24</v>
       </c>
-      <c r="C34" s="18"/>
+      <c r="C34" s="17"/>
     </row>
     <row r="35" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="39" t="s">
+      <c r="A35" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="66">
+      <c r="B35" s="32">
         <f>COUNTIF('Test case'!D7:D500,"PASS")</f>
-        <v>13</v>
-      </c>
-      <c r="C35" s="40">
-        <f>B35/B34%</f>
-        <v>54.166666666666671</v>
+        <v>12</v>
+      </c>
+      <c r="C35" s="64">
+        <f>B35/B34</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="5">
         <f>COUNTIF('Test case'!D7:D500,"FAIL")</f>
-        <v>6</v>
-      </c>
-      <c r="C36" s="18">
-        <f>B36/B34%</f>
-        <v>25</v>
+        <v>7</v>
+      </c>
+      <c r="C36" s="65">
+        <f>B36/B34</f>
+        <v>0.29166666666666669</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="18" t="s">
-        <v>301</v>
+      <c r="A37" s="17" t="s">
+        <v>277</v>
       </c>
       <c r="B37" s="1">
         <f>COUNTIF('Test case'!D7:D500,"IGNORED")</f>
         <v>5</v>
       </c>
-      <c r="C37" s="18">
-        <f>B37/B34%</f>
-        <v>20.833333333333336</v>
+      <c r="C37" s="65">
+        <f>B37/B34</f>
+        <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="18" t="str">
+      <c r="B38" s="17" t="str">
         <f>IF(B36&gt;0, "FAIL", "PASS")</f>
         <v>FAIL</v>
       </c>
-      <c r="C38" s="18"/>
+      <c r="C38" s="17"/>
     </row>
     <row r="40" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="19" t="s">
+      <c r="A40" s="18" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="59" t="s">
+      <c r="C41" s="35" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="17" t="s">
         <v>37</v>
       </c>
       <c r="B42" s="1">
         <f>COUNTIF('Báo cáo lỗi'!$C12:$C499,"Critical")</f>
         <v>4</v>
       </c>
-      <c r="C42" s="53" t="s">
+      <c r="C42" s="33" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="18" t="s">
+      <c r="A43" s="17" t="s">
         <v>39</v>
       </c>
       <c r="B43" s="1">
         <f>COUNTIF('Báo cáo lỗi'!$C13:$C500,"High")</f>
-        <v>2</v>
-      </c>
-      <c r="C43" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="33" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="2">
         <f>COUNTIF('Báo cáo lỗi'!$C13:$C500,"Medium")</f>
         <v>0</v>
       </c>
-      <c r="C44" s="60" t="s">
+      <c r="C44" s="34" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="51" t="s">
+      <c r="A45" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="50">
+      <c r="B45" s="30">
         <f>COUNTIF('Báo cáo lỗi'!$C13:$C500,"Low")</f>
         <v>0</v>
       </c>
-      <c r="C45" s="61" t="s">
+      <c r="C45" s="36" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="67" t="s">
-        <v>302</v>
-      </c>
-      <c r="B46" s="52">
+      <c r="A46" s="40" t="s">
+        <v>278</v>
+      </c>
+      <c r="B46" s="32">
         <f>SUM(B42:B45)</f>
-        <v>6</v>
-      </c>
-      <c r="C46" s="62"/>
+        <v>7</v>
+      </c>
+      <c r="C46" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3486,606 +3660,560 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C715E68-684C-462B-B172-F4A9F2A17487}">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="49.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.90625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="75.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="97.7265625" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.7265625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="8"/>
+    <col min="1" max="1" width="49.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.90625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="41.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="75.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="97.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
+      <c r="A2" s="88" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="88"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="58" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="77" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="11"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="78"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="13"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="78"/>
+      <c r="B6" s="78"/>
+      <c r="C6" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="25" t="s">
+      <c r="D6" s="78"/>
+      <c r="E6" s="9"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="78"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="78"/>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="87"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D8" s="87"/>
+      <c r="E8" s="13"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="77" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4" s="12"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="14"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="15" t="s">
+      <c r="C9" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="12"/>
-    </row>
-    <row r="8" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="16" t="s">
+      <c r="D9" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="9"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="78"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="11"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="78"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="14"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="25" t="s">
+      <c r="D11" s="78"/>
+      <c r="E11" s="13"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="78"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="9"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="78"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="D13" s="78"/>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="78"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="13"/>
+    </row>
+    <row r="15" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="87"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="12"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="15" t="s">
+      <c r="D15" s="87"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="77" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="14"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="15" t="s">
+      <c r="C16" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="12"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="14"/>
-    </row>
-    <row r="15" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="27"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="16" t="s">
+      <c r="D16" s="77" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="78"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="13"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="78"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="27"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="25" t="s">
+      <c r="D18" s="78"/>
+      <c r="E18" s="13"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="78"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="13"/>
+    </row>
+    <row r="20" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="87"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="D20" s="87"/>
+      <c r="E20" s="13"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="77" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="77" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" s="13"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="78"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="78"/>
+    </row>
+    <row r="23" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="87"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="25" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="26"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="14"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="26"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="15" t="s">
+      <c r="D23" s="87"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="88" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="88"/>
+    </row>
+    <row r="28" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="59" t="s">
+        <v>358</v>
+      </c>
+      <c r="B28" s="59" t="s">
+        <v>359</v>
+      </c>
+      <c r="C28" s="59" t="s">
+        <v>360</v>
+      </c>
+      <c r="D28" s="59" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="57" t="s">
+        <v>362</v>
+      </c>
+      <c r="C29" s="57" t="s">
+        <v>363</v>
+      </c>
+      <c r="D29" s="57" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="57" t="s">
+        <v>365</v>
+      </c>
+      <c r="C30" s="57" t="s">
+        <v>366</v>
+      </c>
+      <c r="D30" s="57" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="57" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="57" t="s">
+        <v>368</v>
+      </c>
+      <c r="C31" s="57" t="s">
+        <v>369</v>
+      </c>
+      <c r="D31" s="57" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+    </row>
+    <row r="34" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="D18" s="26"/>
-      <c r="E18" s="14"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="26"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="14"/>
-    </row>
-    <row r="20" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="27"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="16" t="s">
+    </row>
+    <row r="35" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="14"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="E21" s="14"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="26"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="26"/>
-    </row>
-    <row r="23" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="27"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="16" t="s">
+      <c r="B35" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="27"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="42"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="B27" s="28"/>
-    </row>
-    <row r="28" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="9" t="s">
+      <c r="C35" s="58" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="D35" s="58" t="s">
         <v>80</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="E35" s="58" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" s="18" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="B36" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="C36" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="18" t="s">
+      <c r="E36" s="77" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="78"/>
+      <c r="B37" s="78"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="78"/>
+    </row>
+    <row r="38" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="87"/>
+      <c r="B38" s="87"/>
+      <c r="C38" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C30" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D30" s="18" t="s">
+      <c r="E38" s="87"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" s="77" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B31" s="18" t="s">
+      <c r="B39" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="C31" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="18" t="s">
+      <c r="C39" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" s="10" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="42"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-    </row>
-    <row r="34" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="17" t="s">
+      <c r="E39" s="77" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" s="78"/>
+      <c r="B40" s="78"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="78"/>
+    </row>
+    <row r="41" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="87"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41" s="87"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="77" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="9" t="s">
+      <c r="B42" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="C42" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="E42" s="77" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="78"/>
+      <c r="B43" s="78"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="78"/>
+    </row>
+    <row r="44" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="87"/>
+      <c r="B44" s="87"/>
+      <c r="C44" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D44" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="E44" s="87"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="B45" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="C45" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45" s="77" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="78"/>
+      <c r="B46" s="78"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="78"/>
+    </row>
+    <row r="47" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="87"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="B36" s="25" t="s">
+      <c r="D47" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C36" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E36" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="26"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-    </row>
-    <row r="38" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="27"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D38" s="16" t="s">
+      <c r="E47" s="87"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="77" t="s">
         <v>99</v>
       </c>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="25" t="s">
+      <c r="B48" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="C48" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="D48" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C39" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D39" s="11" t="s">
+      <c r="E48" s="77" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="78"/>
+      <c r="B49" s="78"/>
+      <c r="C49" s="78"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="78"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="78"/>
+      <c r="B50" s="78"/>
+      <c r="C50" s="78"/>
+      <c r="D50" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="E50" s="78"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="78"/>
+      <c r="B51" s="78"/>
+      <c r="C51" s="78"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="78"/>
+    </row>
+    <row r="52" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="87"/>
+      <c r="B52" s="87"/>
+      <c r="C52" s="87"/>
+      <c r="D52" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E39" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="26"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-    </row>
-    <row r="41" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="27"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="25" t="s">
+      <c r="E52" s="87"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B53" s="77" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D42" s="11" t="s">
+      <c r="C53" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E53" s="77" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="78"/>
+      <c r="B54" s="78"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="78"/>
+    </row>
+    <row r="55" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="87"/>
+      <c r="B55" s="87"/>
+      <c r="C55" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="E42" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="26"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
-    </row>
-    <row r="44" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="27"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="25" t="s">
+      <c r="D55" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="E45" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="26"/>
-      <c r="B46" s="26"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-    </row>
-    <row r="47" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="27"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="B48" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E48" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" s="26"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50" s="26"/>
-      <c r="B50" s="26"/>
-      <c r="C50" s="26"/>
-      <c r="D50" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E50" s="26"/>
-      <c r="F50" s="26"/>
-      <c r="G50" s="26"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51" s="26"/>
-      <c r="B51" s="26"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="26"/>
-      <c r="G51" s="26"/>
-    </row>
-    <row r="52" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="27"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="B53" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="E53" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="F53" s="25"/>
-      <c r="G53" s="25"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="26"/>
-      <c r="B54" s="26"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-    </row>
-    <row r="55" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="27"/>
-      <c r="B55" s="27"/>
-      <c r="C55" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
+      <c r="E55" s="87"/>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="33">
     <mergeCell ref="D16:D20"/>
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="B21:B23"/>
@@ -4096,27 +4224,16 @@
     <mergeCell ref="A9:A15"/>
     <mergeCell ref="B9:B15"/>
     <mergeCell ref="D9:D15"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="E45:E47"/>
     <mergeCell ref="E36:E38"/>
-    <mergeCell ref="F36:F38"/>
-    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="B39:B41"/>
     <mergeCell ref="E39:E41"/>
-    <mergeCell ref="F39:F41"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="E48:E52"/>
-    <mergeCell ref="F48:F52"/>
-    <mergeCell ref="G48:G52"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="E45:E47"/>
-    <mergeCell ref="F45:F47"/>
-    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="E53:E55"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A48:A52"/>
@@ -4126,11 +4243,10 @@
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="A16:A20"/>
     <mergeCell ref="B16:B20"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="E53:E55"/>
-    <mergeCell ref="F53:F55"/>
-    <mergeCell ref="G53:G55"/>
+    <mergeCell ref="E48:E52"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="E42:E44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4138,91 +4254,91 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7741C703-A867-48A4-AF61-54AA66C0FB72}">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="38.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="73.90625" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.90625" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="7"/>
+    <col min="1" max="1" width="38.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.6328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="73.90625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.90625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
-        <v>142</v>
+      <c r="A1" s="23" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="B2" s="32"/>
+      <c r="A2" s="66" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="66"/>
     </row>
     <row r="3" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>148</v>
+      <c r="A3" s="62" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="62" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E4" s="36">
+      <c r="A4" s="67" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E4" s="74">
         <v>1234.56</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="37"/>
+      <c r="A5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="75"/>
     </row>
     <row r="6" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="31"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="E6" s="38"/>
+      <c r="A6" s="69"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6" s="76"/>
     </row>
     <row r="7" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E7" s="21">
+        <v>182</v>
+      </c>
+      <c r="E7" s="20">
         <v>45291</v>
       </c>
     </row>
@@ -4230,444 +4346,637 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>155</v>
+      <c r="A9" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" s="67" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="70" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="30"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="34"/>
+      <c r="A10" s="68"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="71"/>
     </row>
     <row r="11" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E11" s="35"/>
+      <c r="A11" s="69"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" s="72"/>
     </row>
     <row r="12" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>156</v>
+        <v>185</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>204</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>158</v>
+      <c r="A13" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="67" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E13" s="70" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="34"/>
+      <c r="A14" s="68"/>
+      <c r="B14" s="68"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="71"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E15" s="34"/>
+      <c r="A15" s="68"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E15" s="71"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="34"/>
-    </row>
-    <row r="17" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E17" s="35"/>
-    </row>
-    <row r="18" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="68"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="71"/>
+    </row>
+    <row r="17" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="69"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E17" s="72"/>
+    </row>
+    <row r="18" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="B19" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="C19" s="67" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E19" s="67" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="68"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="68"/>
+    </row>
+    <row r="21" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="69"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E21" s="69"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="46"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+    </row>
+    <row r="23" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="73" t="s">
+        <v>371</v>
+      </c>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+    </row>
+    <row r="24" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="63" t="s">
+        <v>372</v>
+      </c>
+      <c r="B24" s="63" t="s">
+        <v>373</v>
+      </c>
+      <c r="C24" s="63" t="s">
+        <v>374</v>
+      </c>
+      <c r="D24" s="63" t="s">
+        <v>375</v>
+      </c>
+      <c r="E24" s="63" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="57" t="s">
+        <v>377</v>
+      </c>
+      <c r="B25" s="60" t="s">
+        <v>378</v>
+      </c>
+      <c r="C25" s="60" t="s">
+        <v>379</v>
+      </c>
+      <c r="D25" s="60" t="s">
+        <v>379</v>
+      </c>
+      <c r="E25" s="60" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="57" t="s">
+        <v>380</v>
+      </c>
+      <c r="B26" s="60" t="s">
+        <v>379</v>
+      </c>
+      <c r="C26" s="60" t="s">
+        <v>378</v>
+      </c>
+      <c r="D26" s="60" t="s">
+        <v>379</v>
+      </c>
+      <c r="E26" s="60" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="57" t="s">
+        <v>381</v>
+      </c>
+      <c r="B27" s="60" t="s">
+        <v>379</v>
+      </c>
+      <c r="C27" s="60" t="s">
+        <v>379</v>
+      </c>
+      <c r="D27" s="60" t="s">
+        <v>378</v>
+      </c>
+      <c r="E27" s="60" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="57" t="s">
+        <v>382</v>
+      </c>
+      <c r="B28" s="60" t="s">
+        <v>379</v>
+      </c>
+      <c r="C28" s="60" t="s">
+        <v>379</v>
+      </c>
+      <c r="D28" s="60" t="s">
+        <v>379</v>
+      </c>
+      <c r="E28" s="60" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="61"/>
+      <c r="B29" s="61"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="61"/>
+    </row>
+    <row r="30" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="73" t="s">
+        <v>383</v>
+      </c>
+      <c r="B30" s="73"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
+    </row>
+    <row r="31" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="63" t="s">
+        <v>384</v>
+      </c>
+      <c r="B31" s="63" t="s">
+        <v>373</v>
+      </c>
+      <c r="C31" s="63" t="s">
+        <v>374</v>
+      </c>
+      <c r="D31" s="63" t="s">
+        <v>375</v>
+      </c>
+      <c r="E31" s="63" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="57" t="s">
+        <v>385</v>
+      </c>
+      <c r="B32" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+    </row>
+    <row r="33" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="57" t="s">
+        <v>387</v>
+      </c>
+      <c r="B33" s="60"/>
+      <c r="C33" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="D33" s="60"/>
+      <c r="E33" s="60"/>
+    </row>
+    <row r="34" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="57" t="s">
+        <v>388</v>
+      </c>
+      <c r="B34" s="60"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="E34" s="60"/>
+    </row>
+    <row r="35" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="57" t="s">
+        <v>389</v>
+      </c>
+      <c r="B35" s="60"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="57" t="s">
+        <v>390</v>
+      </c>
+      <c r="B36" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="C36" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="D36" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="E36" s="60"/>
+    </row>
+    <row r="37" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="57" t="s">
+        <v>391</v>
+      </c>
+      <c r="B37" s="60"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="57" t="s">
+        <v>392</v>
+      </c>
+      <c r="B38" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="C38" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="D38" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="E38" s="60"/>
+    </row>
+    <row r="39" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="57" t="s">
+        <v>393</v>
+      </c>
+      <c r="B39" s="60"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="46"/>
+      <c r="B40" s="46"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="46"/>
+    </row>
+    <row r="41" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" s="62" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" s="62" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" s="62" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="F42" s="62" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="67" t="s">
+        <v>150</v>
+      </c>
+      <c r="B43" s="67" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E18" s="22" t="s">
+      <c r="D43" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F43" s="67" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="68"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="68"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="68"/>
+    </row>
+    <row r="45" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="69"/>
+      <c r="B45" s="69"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F45" s="69"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="67" t="s">
+        <v>153</v>
+      </c>
+      <c r="B46" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="67" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="68"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="68"/>
+    </row>
+    <row r="48" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="69"/>
+      <c r="B48" s="69"/>
+      <c r="C48" s="69"/>
+      <c r="D48" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F48" s="69"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="67" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="29" t="s">
+      <c r="B49" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49" s="67" t="s">
+        <v>157</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F49" s="67" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="68"/>
+      <c r="B50" s="68"/>
+      <c r="C50" s="68"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="68"/>
+    </row>
+    <row r="51" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="69"/>
+      <c r="B51" s="69"/>
+      <c r="C51" s="69"/>
+      <c r="D51" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F51" s="69"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="B52" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="B19" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="C19" s="29" t="s">
+      <c r="C52" s="67" t="s">
         <v>160</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E19" s="29" t="s">
+      <c r="D52" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="30"/>
-    </row>
-    <row r="21" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="E21" s="31"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="76"/>
-      <c r="B22" s="76"/>
-      <c r="C22" s="76"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
-    </row>
-    <row r="24" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="24" t="s">
+      <c r="F52" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="68"/>
+      <c r="B53" s="68"/>
+      <c r="C53" s="68"/>
+      <c r="D53" s="68"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="68"/>
+      <c r="B54" s="68"/>
+      <c r="C54" s="68"/>
+      <c r="D54" s="68"/>
+      <c r="E54" s="3" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="F54" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="68"/>
+      <c r="B55" s="68"/>
+      <c r="C55" s="68"/>
+      <c r="D55" s="68"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="69"/>
+      <c r="B56" s="69"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="69"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="29" t="s">
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="B26" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="C26" s="29" t="s">
+      <c r="B57" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="C57" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="F26" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-    </row>
-    <row r="28" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="31"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="B29" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="C29" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="F29" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="30"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-    </row>
-    <row r="31" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="31"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="B32" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F32" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="30"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-    </row>
-    <row r="34" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="31"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="B35" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="C35" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="D35" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="30"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="30"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="4" t="s">
+      <c r="D57" s="67" t="s">
         <v>176</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="30"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-    </row>
-    <row r="39" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="31"/>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="6" t="s">
+      <c r="E57" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="29" t="s">
+      <c r="F57" s="67" t="s">
         <v>178</v>
       </c>
-      <c r="B40" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="C40" s="29" t="s">
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="68"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="68"/>
+      <c r="D58" s="68"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="68"/>
+    </row>
+    <row r="59" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="69"/>
+      <c r="B59" s="69"/>
+      <c r="C59" s="69"/>
+      <c r="D59" s="69"/>
+      <c r="E59" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D40" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F40" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="30"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-    </row>
-    <row r="42" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="31"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
+      <c r="F59" s="69"/>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="40">
+    <mergeCell ref="F43:F45"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:C6"/>
@@ -4676,46 +4985,35 @@
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="E9:E11"/>
-    <mergeCell ref="H26:H28"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C13:C17"/>
     <mergeCell ref="E13:E17"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="C19:C21"/>
     <mergeCell ref="E19:E21"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="H32:H34"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="F29:F31"/>
-    <mergeCell ref="G29:G31"/>
-    <mergeCell ref="H29:H31"/>
-    <mergeCell ref="H40:H42"/>
+    <mergeCell ref="F49:F51"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="F57:F59"/>
+    <mergeCell ref="A52:A56"/>
+    <mergeCell ref="B52:B56"/>
+    <mergeCell ref="C52:C56"/>
+    <mergeCell ref="D52:D56"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="F40:F42"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="A35:A39"/>
-    <mergeCell ref="B35:B39"/>
-    <mergeCell ref="C35:C39"/>
-    <mergeCell ref="D35:D39"/>
-    <mergeCell ref="G35:G39"/>
-    <mergeCell ref="H35:H39"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="C43:C45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4726,975 +5024,977 @@
   <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12" style="70" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35" style="70" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="70" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" style="70" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.36328125" style="70" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.36328125" style="70" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="64.1796875" style="70" customWidth="1"/>
-    <col min="8" max="8" width="70.1796875" style="70" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="66.81640625" style="70" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.7265625" style="70"/>
+    <col min="1" max="1" width="12" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.36328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64.1796875" style="28" customWidth="1"/>
+    <col min="8" max="8" width="70.1796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="66.81640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.7265625" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="89" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="29"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="55" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="55" t="s">
+        <v>208</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="G3" s="29"/>
+      <c r="H3" s="55" t="s">
+        <v>210</v>
+      </c>
+      <c r="I3" s="29" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="29"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="91" t="s">
+        <v>212</v>
+      </c>
+      <c r="B5" s="92"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>220</v>
+      </c>
+      <c r="I6" s="41" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="42">
+        <v>1</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>224</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="G7" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="H7" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="42">
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>228</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="H8" s="42"/>
+      <c r="I8" s="29" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="42">
+        <v>3</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>230</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="H9" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="42">
+        <v>4</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="H10" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="I10" s="29" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="42">
+        <v>5</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>239</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="42">
+        <v>6</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="D12" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>241</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="I12" s="29" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="42">
+        <v>7</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="42">
+        <v>8</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>244</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="42">
+        <v>9</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>297</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="H15" s="42"/>
+      <c r="I15" s="29" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="42">
+        <v>10</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>297</v>
+      </c>
+      <c r="G16" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="H16" s="42"/>
+      <c r="I16" s="29" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="42">
+        <v>11</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>245</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>297</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="H17" s="42"/>
+      <c r="I17" s="29" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="42">
+        <v>12</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>245</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>250</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="H18" s="42" t="s">
+        <v>252</v>
+      </c>
+      <c r="I18" s="29" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="42">
+        <v>13</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="H19" s="42"/>
+      <c r="I19" s="29" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="42">
+        <v>14</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="G20" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="H20" s="42"/>
+      <c r="I20" s="29" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="42">
+        <v>15</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>256</v>
+      </c>
+      <c r="F21" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="G21" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="H21" s="42"/>
+      <c r="I21" s="29" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="42">
+        <v>16</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="F22" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="G22" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="H22" s="42"/>
+      <c r="I22" s="29" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="42">
+        <v>17</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="D23" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="G23" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="H23" s="42"/>
+      <c r="I23" s="29" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="42">
+        <v>18</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="C24" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="D24" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="F24" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="G24" s="29" t="s">
+        <v>401</v>
+      </c>
+      <c r="H24" s="42" t="s">
+        <v>404</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="42">
+        <v>19</v>
+      </c>
+      <c r="B25" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="F25" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="G25" s="29" t="s">
+        <v>402</v>
+      </c>
+      <c r="H25" s="42" t="s">
+        <v>405</v>
+      </c>
+      <c r="I25" s="29" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="42">
+        <v>20</v>
+      </c>
+      <c r="B26" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="F26" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="G26" s="29" t="s">
+        <v>403</v>
+      </c>
+      <c r="H26" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="I26" s="29" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="42">
+        <v>21</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="G27" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="H27" s="42"/>
+      <c r="I27" s="29" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="42">
+        <v>22</v>
+      </c>
+      <c r="B28" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="G28" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="H28" s="42"/>
+      <c r="I28" s="29" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="42">
+        <v>23</v>
+      </c>
+      <c r="B29" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E29" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="F29" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="G29" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="H29" s="42"/>
+      <c r="I29" s="29" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="42">
+        <v>24</v>
+      </c>
+      <c r="B30" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="D30" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E30" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="F30" s="29" t="s">
         <v>307</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="41"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="49"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="B3" s="49" t="s">
-        <v>222</v>
-      </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="87" t="s">
-        <v>223</v>
-      </c>
-      <c r="F3" s="49" t="s">
-        <v>224</v>
-      </c>
-      <c r="G3" s="49"/>
-      <c r="H3" s="87" t="s">
-        <v>225</v>
-      </c>
-      <c r="I3" s="49" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="49"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="88" t="s">
-        <v>227</v>
-      </c>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="71" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6" s="71" t="s">
-        <v>229</v>
-      </c>
-      <c r="C6" s="71" t="s">
-        <v>230</v>
-      </c>
-      <c r="D6" s="71" t="s">
-        <v>231</v>
-      </c>
-      <c r="E6" s="71" t="s">
-        <v>232</v>
-      </c>
-      <c r="F6" s="71" t="s">
-        <v>233</v>
-      </c>
-      <c r="G6" s="71" t="s">
-        <v>234</v>
-      </c>
-      <c r="H6" s="71" t="s">
-        <v>235</v>
-      </c>
-      <c r="I6" s="71" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="72">
-        <v>1</v>
-      </c>
-      <c r="B7" s="72" t="s">
-        <v>237</v>
-      </c>
-      <c r="C7" s="72" t="s">
-        <v>238</v>
-      </c>
-      <c r="D7" s="73" t="s">
-        <v>207</v>
-      </c>
-      <c r="E7" s="72" t="s">
-        <v>239</v>
-      </c>
-      <c r="F7" s="72" t="s">
-        <v>240</v>
-      </c>
-      <c r="G7" s="72" t="s">
-        <v>244</v>
-      </c>
-      <c r="H7" s="72" t="s">
-        <v>241</v>
-      </c>
-      <c r="I7" s="90" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="72">
-        <v>2</v>
-      </c>
-      <c r="B8" s="72" t="s">
-        <v>237</v>
-      </c>
-      <c r="C8" s="72" t="s">
-        <v>242</v>
-      </c>
-      <c r="D8" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="E8" s="72" t="s">
-        <v>243</v>
-      </c>
-      <c r="F8" s="72" t="s">
-        <v>244</v>
-      </c>
-      <c r="G8" s="72" t="s">
-        <v>244</v>
-      </c>
-      <c r="H8" s="72"/>
-      <c r="I8" s="90" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="72">
-        <v>3</v>
-      </c>
-      <c r="B9" s="72" t="s">
-        <v>237</v>
-      </c>
-      <c r="C9" s="72" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="73" t="s">
-        <v>207</v>
-      </c>
-      <c r="E9" s="72" t="s">
-        <v>245</v>
-      </c>
-      <c r="F9" s="72" t="s">
-        <v>246</v>
-      </c>
-      <c r="G9" s="72" t="s">
-        <v>244</v>
-      </c>
-      <c r="H9" s="72" t="s">
-        <v>247</v>
-      </c>
-      <c r="I9" s="90" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="72">
-        <v>4</v>
-      </c>
-      <c r="B10" s="72" t="s">
-        <v>237</v>
-      </c>
-      <c r="C10" s="72" t="s">
-        <v>248</v>
-      </c>
-      <c r="D10" s="73" t="s">
-        <v>207</v>
-      </c>
-      <c r="E10" s="72" t="s">
-        <v>249</v>
-      </c>
-      <c r="F10" s="72" t="s">
-        <v>250</v>
-      </c>
-      <c r="G10" s="72" t="s">
-        <v>244</v>
-      </c>
-      <c r="H10" s="72" t="s">
-        <v>251</v>
-      </c>
-      <c r="I10" s="90" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="72">
-        <v>5</v>
-      </c>
-      <c r="B11" s="72" t="s">
-        <v>252</v>
-      </c>
-      <c r="C11" s="72" t="s">
-        <v>238</v>
-      </c>
-      <c r="D11" s="75" t="s">
-        <v>253</v>
-      </c>
-      <c r="E11" s="72" t="s">
-        <v>254</v>
-      </c>
-      <c r="F11" s="72" t="s">
-        <v>255</v>
-      </c>
-      <c r="G11" s="90" t="s">
-        <v>316</v>
-      </c>
-      <c r="H11" s="90" t="s">
-        <v>317</v>
-      </c>
-      <c r="I11" s="90" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="72">
-        <v>6</v>
-      </c>
-      <c r="B12" s="72" t="s">
-        <v>252</v>
-      </c>
-      <c r="C12" s="72" t="s">
-        <v>242</v>
-      </c>
-      <c r="D12" s="75" t="s">
-        <v>253</v>
-      </c>
-      <c r="E12" s="72" t="s">
-        <v>256</v>
-      </c>
-      <c r="F12" s="72" t="s">
-        <v>257</v>
-      </c>
-      <c r="G12" s="90" t="s">
-        <v>316</v>
-      </c>
-      <c r="H12" s="90" t="s">
-        <v>317</v>
-      </c>
-      <c r="I12" s="90" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="72">
-        <v>7</v>
-      </c>
-      <c r="B13" s="72" t="s">
-        <v>252</v>
-      </c>
-      <c r="C13" s="72" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="75" t="s">
-        <v>253</v>
-      </c>
-      <c r="E13" s="72" t="s">
-        <v>258</v>
-      </c>
-      <c r="F13" s="72" t="s">
-        <v>257</v>
-      </c>
-      <c r="G13" s="90" t="s">
-        <v>316</v>
-      </c>
-      <c r="H13" s="90" t="s">
-        <v>317</v>
-      </c>
-      <c r="I13" s="90" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="72">
-        <v>8</v>
-      </c>
-      <c r="B14" s="72" t="s">
-        <v>252</v>
-      </c>
-      <c r="C14" s="72" t="s">
-        <v>248</v>
-      </c>
-      <c r="D14" s="75" t="s">
-        <v>253</v>
-      </c>
-      <c r="E14" s="72" t="s">
-        <v>259</v>
-      </c>
-      <c r="F14" s="72" t="s">
-        <v>257</v>
-      </c>
-      <c r="G14" s="90" t="s">
-        <v>316</v>
-      </c>
-      <c r="H14" s="90" t="s">
-        <v>317</v>
-      </c>
-      <c r="I14" s="90" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="72">
-        <v>9</v>
-      </c>
-      <c r="B15" s="72" t="s">
-        <v>260</v>
-      </c>
-      <c r="C15" s="72" t="s">
-        <v>238</v>
-      </c>
-      <c r="D15" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="E15" s="72" t="s">
-        <v>261</v>
-      </c>
-      <c r="F15" s="90" t="s">
-        <v>322</v>
-      </c>
-      <c r="G15" s="72" t="s">
-        <v>262</v>
-      </c>
-      <c r="H15" s="72"/>
-      <c r="I15" s="90" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="72">
-        <v>10</v>
-      </c>
-      <c r="B16" s="72" t="s">
-        <v>260</v>
-      </c>
-      <c r="C16" s="72" t="s">
-        <v>242</v>
-      </c>
-      <c r="D16" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="E16" s="72" t="s">
-        <v>263</v>
-      </c>
-      <c r="F16" s="90" t="s">
-        <v>322</v>
-      </c>
-      <c r="G16" s="72" t="s">
-        <v>262</v>
-      </c>
-      <c r="H16" s="72"/>
-      <c r="I16" s="90" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="72">
-        <v>11</v>
-      </c>
-      <c r="B17" s="72" t="s">
-        <v>260</v>
-      </c>
-      <c r="C17" s="72" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="E17" s="72" t="s">
-        <v>264</v>
-      </c>
-      <c r="F17" s="90" t="s">
-        <v>322</v>
-      </c>
-      <c r="G17" s="72" t="s">
-        <v>262</v>
-      </c>
-      <c r="H17" s="72"/>
-      <c r="I17" s="90" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="72">
-        <v>12</v>
-      </c>
-      <c r="B18" s="72" t="s">
-        <v>260</v>
-      </c>
-      <c r="C18" s="72" t="s">
-        <v>248</v>
-      </c>
-      <c r="D18" s="73" t="s">
-        <v>207</v>
-      </c>
-      <c r="E18" s="72" t="s">
-        <v>265</v>
-      </c>
-      <c r="F18" s="90" t="s">
-        <v>321</v>
-      </c>
-      <c r="G18" s="72" t="s">
-        <v>266</v>
-      </c>
-      <c r="H18" s="72" t="s">
-        <v>267</v>
-      </c>
-      <c r="I18" s="90" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="72">
-        <v>13</v>
-      </c>
-      <c r="B19" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="C19" s="72" t="s">
-        <v>238</v>
-      </c>
-      <c r="D19" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="E19" s="72" t="s">
-        <v>269</v>
-      </c>
-      <c r="F19" s="90" t="s">
-        <v>319</v>
-      </c>
-      <c r="G19" s="72" t="s">
-        <v>270</v>
-      </c>
-      <c r="H19" s="72"/>
-      <c r="I19" s="90" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="72">
-        <v>14</v>
-      </c>
-      <c r="B20" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="C20" s="72" t="s">
-        <v>242</v>
-      </c>
-      <c r="D20" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="E20" s="72" t="s">
-        <v>269</v>
-      </c>
-      <c r="F20" s="90" t="s">
-        <v>319</v>
-      </c>
-      <c r="G20" s="72" t="s">
-        <v>270</v>
-      </c>
-      <c r="H20" s="72"/>
-      <c r="I20" s="90" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="72">
-        <v>15</v>
-      </c>
-      <c r="B21" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="C21" s="72" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="E21" s="72" t="s">
-        <v>271</v>
-      </c>
-      <c r="F21" s="90" t="s">
-        <v>319</v>
-      </c>
-      <c r="G21" s="72" t="s">
-        <v>270</v>
-      </c>
-      <c r="H21" s="72"/>
-      <c r="I21" s="90" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="72">
-        <v>16</v>
-      </c>
-      <c r="B22" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="C22" s="72" t="s">
-        <v>248</v>
-      </c>
-      <c r="D22" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="E22" s="72" t="s">
-        <v>272</v>
-      </c>
-      <c r="F22" s="90" t="s">
-        <v>319</v>
-      </c>
-      <c r="G22" s="72" t="s">
-        <v>270</v>
-      </c>
-      <c r="H22" s="72"/>
-      <c r="I22" s="90" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="72">
-        <v>17</v>
-      </c>
-      <c r="B23" s="72" t="s">
-        <v>273</v>
-      </c>
-      <c r="C23" s="72" t="s">
-        <v>238</v>
-      </c>
-      <c r="D23" s="75" t="s">
-        <v>253</v>
-      </c>
-      <c r="E23" s="72" t="s">
-        <v>274</v>
-      </c>
-      <c r="F23" s="90" t="s">
-        <v>323</v>
-      </c>
-      <c r="G23" s="72" t="s">
-        <v>324</v>
-      </c>
-      <c r="H23" s="72"/>
-      <c r="I23" s="90" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="72">
-        <v>18</v>
-      </c>
-      <c r="B24" s="72" t="s">
-        <v>273</v>
-      </c>
-      <c r="C24" s="72" t="s">
-        <v>242</v>
-      </c>
-      <c r="D24" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="E24" s="72" t="s">
-        <v>275</v>
-      </c>
-      <c r="F24" s="90" t="s">
-        <v>326</v>
-      </c>
-      <c r="G24" s="90" t="s">
-        <v>327</v>
-      </c>
-      <c r="H24" s="72"/>
-      <c r="I24" s="90" t="s">
+      <c r="G30" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="H30" s="42"/>
+      <c r="I30" s="29" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="72">
-        <v>19</v>
-      </c>
-      <c r="B25" s="72" t="s">
-        <v>273</v>
-      </c>
-      <c r="C25" s="72" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="73" t="s">
-        <v>207</v>
-      </c>
-      <c r="E25" s="72" t="s">
-        <v>276</v>
-      </c>
-      <c r="F25" s="90" t="s">
-        <v>326</v>
-      </c>
-      <c r="G25" s="90" t="s">
-        <v>328</v>
-      </c>
-      <c r="H25" s="72" t="s">
-        <v>277</v>
-      </c>
-      <c r="I25" s="90" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="72">
-        <v>20</v>
-      </c>
-      <c r="B26" s="72" t="s">
-        <v>273</v>
-      </c>
-      <c r="C26" s="72" t="s">
-        <v>248</v>
-      </c>
-      <c r="D26" s="73" t="s">
-        <v>207</v>
-      </c>
-      <c r="E26" s="72" t="s">
-        <v>278</v>
-      </c>
-      <c r="F26" s="90" t="s">
-        <v>326</v>
-      </c>
-      <c r="G26" s="90" t="s">
-        <v>329</v>
-      </c>
-      <c r="H26" s="72" t="s">
-        <v>279</v>
-      </c>
-      <c r="I26" s="90" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="72">
-        <v>21</v>
-      </c>
-      <c r="B27" s="72" t="s">
-        <v>280</v>
-      </c>
-      <c r="C27" s="72" t="s">
-        <v>238</v>
-      </c>
-      <c r="D27" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="E27" s="72" t="s">
-        <v>281</v>
-      </c>
-      <c r="F27" s="90" t="s">
-        <v>331</v>
-      </c>
-      <c r="G27" s="90" t="s">
-        <v>332</v>
-      </c>
-      <c r="H27" s="72"/>
-      <c r="I27" s="90" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="72">
-        <v>22</v>
-      </c>
-      <c r="B28" s="72" t="s">
-        <v>280</v>
-      </c>
-      <c r="C28" s="72" t="s">
-        <v>242</v>
-      </c>
-      <c r="D28" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="E28" s="72" t="s">
-        <v>263</v>
-      </c>
-      <c r="F28" s="90" t="s">
-        <v>333</v>
-      </c>
-      <c r="G28" s="90" t="s">
-        <v>332</v>
-      </c>
-      <c r="H28" s="72"/>
-      <c r="I28" s="90" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="72">
-        <v>23</v>
-      </c>
-      <c r="B29" s="72" t="s">
-        <v>280</v>
-      </c>
-      <c r="C29" s="72" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="E29" s="72" t="s">
-        <v>282</v>
-      </c>
-      <c r="F29" s="90" t="s">
-        <v>334</v>
-      </c>
-      <c r="G29" s="90" t="s">
-        <v>332</v>
-      </c>
-      <c r="H29" s="72"/>
-      <c r="I29" s="90" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="72">
-        <v>24</v>
-      </c>
-      <c r="B30" s="72" t="s">
-        <v>280</v>
-      </c>
-      <c r="C30" s="72" t="s">
-        <v>248</v>
-      </c>
-      <c r="D30" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="E30" s="72" t="s">
-        <v>276</v>
-      </c>
-      <c r="F30" s="90" t="s">
-        <v>335</v>
-      </c>
-      <c r="G30" s="90" t="s">
-        <v>332</v>
-      </c>
-      <c r="H30" s="72"/>
-      <c r="I30" s="90" t="s">
-        <v>339</v>
-      </c>
-    </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" s="76"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="77"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="76"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
+      <c r="A31" s="46"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" s="76"/>
-      <c r="B32" s="76"/>
-      <c r="C32" s="77"/>
-      <c r="D32" s="76"/>
-      <c r="E32" s="76"/>
-      <c r="F32" s="76"/>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
+      <c r="A32" s="46"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="46"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="76"/>
-      <c r="B33" s="76"/>
-      <c r="C33" s="77"/>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
+      <c r="A33" s="46"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="76"/>
-      <c r="B34" s="76"/>
-      <c r="C34" s="77"/>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
+      <c r="A34" s="46"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="46"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="76"/>
-      <c r="B35" s="76"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
+      <c r="A35" s="46"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="46"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="76"/>
-      <c r="B36" s="76"/>
-      <c r="C36" s="77"/>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
+      <c r="A36" s="46"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="76"/>
-      <c r="B37" s="76"/>
-      <c r="C37" s="77"/>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
+      <c r="A37" s="46"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="46"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="76"/>
-      <c r="B38" s="76"/>
-      <c r="C38" s="77"/>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
+      <c r="A38" s="46"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="46"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="76"/>
-      <c r="B39" s="76"/>
-      <c r="C39" s="77"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="76"/>
+      <c r="A39" s="46"/>
+      <c r="B39" s="46"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="46"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="76"/>
-      <c r="B40" s="76"/>
-      <c r="C40" s="77"/>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="76"/>
-      <c r="H40" s="76"/>
+      <c r="A40" s="46"/>
+      <c r="B40" s="46"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="46"/>
+      <c r="H40" s="46"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="76"/>
-      <c r="B41" s="76"/>
-      <c r="C41" s="77"/>
-      <c r="D41" s="76"/>
-      <c r="E41" s="76"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="76"/>
+      <c r="A41" s="46"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="46"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="76"/>
-      <c r="B42" s="76"/>
-      <c r="C42" s="77"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="76"/>
+      <c r="A42" s="46"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="46"/>
+      <c r="H42" s="46"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="76"/>
-      <c r="B43" s="76"/>
-      <c r="C43" s="77"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="76"/>
+      <c r="A43" s="46"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="47"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="46"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="76"/>
-      <c r="B44" s="76"/>
-      <c r="C44" s="77"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="76"/>
+      <c r="A44" s="46"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="46"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="76"/>
-      <c r="B45" s="76"/>
-      <c r="C45" s="77"/>
-      <c r="D45" s="76"/>
-      <c r="E45" s="76"/>
-      <c r="F45" s="76"/>
-      <c r="G45" s="76"/>
-      <c r="H45" s="76"/>
+      <c r="A45" s="46"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="47"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="46"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="76"/>
-      <c r="B46" s="76"/>
-      <c r="C46" s="77"/>
-      <c r="D46" s="76"/>
-      <c r="E46" s="76"/>
-      <c r="F46" s="76"/>
-      <c r="G46" s="76"/>
-      <c r="H46" s="76"/>
+      <c r="A46" s="46"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="47"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="46"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="76"/>
-      <c r="B47" s="76"/>
-      <c r="C47" s="77"/>
-      <c r="D47" s="76"/>
-      <c r="E47" s="76"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="76"/>
-      <c r="H47" s="76"/>
+      <c r="A47" s="46"/>
+      <c r="B47" s="46"/>
+      <c r="C47" s="47"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="46"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="76"/>
-      <c r="B48" s="76"/>
-      <c r="C48" s="77"/>
-      <c r="D48" s="76"/>
-      <c r="E48" s="76"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="76"/>
-      <c r="H48" s="76"/>
+      <c r="A48" s="46"/>
+      <c r="B48" s="46"/>
+      <c r="C48" s="47"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
+      <c r="G48" s="46"/>
+      <c r="H48" s="46"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="76"/>
-      <c r="B49" s="76"/>
-      <c r="C49" s="77"/>
-      <c r="D49" s="76"/>
-      <c r="E49" s="76"/>
-      <c r="F49" s="76"/>
-      <c r="G49" s="76"/>
-      <c r="H49" s="76"/>
+      <c r="A49" s="46"/>
+      <c r="B49" s="46"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5711,602 +6011,639 @@
   <dimension ref="A1:N49"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12" style="48" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" style="48" customWidth="1"/>
-    <col min="4" max="4" width="12" style="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" style="48" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.7265625" style="48" customWidth="1"/>
-    <col min="7" max="7" width="62.26953125" style="48" customWidth="1"/>
-    <col min="8" max="8" width="40.36328125" style="48" customWidth="1"/>
-    <col min="9" max="9" width="47.54296875" style="48" customWidth="1"/>
-    <col min="10" max="10" width="27.36328125" style="48" customWidth="1"/>
-    <col min="11" max="11" width="32.1796875" style="48" customWidth="1"/>
-    <col min="12" max="12" width="39.26953125" style="48" customWidth="1"/>
-    <col min="13" max="13" width="44.81640625" style="48" customWidth="1"/>
-    <col min="14" max="14" width="14.1796875" style="48" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.7265625" style="48"/>
+    <col min="1" max="1" width="12" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" style="28" customWidth="1"/>
+    <col min="4" max="4" width="12" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.7265625" style="28" customWidth="1"/>
+    <col min="7" max="7" width="62.26953125" style="28" customWidth="1"/>
+    <col min="8" max="8" width="40.36328125" style="28" customWidth="1"/>
+    <col min="9" max="9" width="47.54296875" style="28" customWidth="1"/>
+    <col min="10" max="10" width="27.36328125" style="28" customWidth="1"/>
+    <col min="11" max="11" width="32.1796875" style="28" customWidth="1"/>
+    <col min="12" max="12" width="39.26953125" style="28" customWidth="1"/>
+    <col min="13" max="13" width="44.81640625" style="28" customWidth="1"/>
+    <col min="14" max="14" width="14.1796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.7265625" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" s="78" t="s">
-        <v>212</v>
+      <c r="A1" s="48" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="8"/>
+      <c r="A2" s="7"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>303</v>
+      <c r="A3" s="16" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="8"/>
+      <c r="A4" s="7"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="17" t="s">
-        <v>304</v>
+      <c r="A5" s="16" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="8"/>
+      <c r="A6" s="7"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="17" t="s">
-        <v>305</v>
+      <c r="A7" s="16" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="8"/>
+      <c r="A8" s="7"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="17" t="s">
-        <v>306</v>
+      <c r="A9" s="16" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="79" t="s">
-        <v>283</v>
-      </c>
-      <c r="B11" s="80"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="80"/>
-      <c r="K11" s="80"/>
-      <c r="L11" s="80"/>
-      <c r="M11" s="80"/>
-      <c r="N11" s="80"/>
+      <c r="A11" s="93" t="s">
+        <v>266</v>
+      </c>
+      <c r="B11" s="94"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
+      <c r="E11" s="94"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="94"/>
+      <c r="K11" s="94"/>
+      <c r="L11" s="94"/>
+      <c r="M11" s="94"/>
+      <c r="N11" s="94"/>
     </row>
     <row r="12" spans="1:14" ht="33" x14ac:dyDescent="0.35">
-      <c r="A12" s="81" t="s">
-        <v>213</v>
-      </c>
-      <c r="B12" s="81" t="s">
+      <c r="A12" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>267</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>312</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="E12" s="49" t="s">
+        <v>313</v>
+      </c>
+      <c r="F12" s="49" t="s">
+        <v>314</v>
+      </c>
+      <c r="G12" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="H12" s="49" t="s">
+        <v>316</v>
+      </c>
+      <c r="I12" s="49" t="s">
+        <v>317</v>
+      </c>
+      <c r="J12" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="K12" s="49" t="s">
         <v>284</v>
       </c>
-      <c r="C12" s="81" t="s">
+      <c r="L12" s="49" t="s">
+        <v>318</v>
+      </c>
+      <c r="M12" s="49" t="s">
+        <v>319</v>
+      </c>
+      <c r="N12" s="49" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="50" t="s">
+        <v>268</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>395</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>269</v>
+      </c>
+      <c r="F13" s="50" t="s">
+        <v>322</v>
+      </c>
+      <c r="G13" s="50" t="s">
+        <v>323</v>
+      </c>
+      <c r="H13" s="50" t="s">
+        <v>324</v>
+      </c>
+      <c r="I13" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="J13" s="50" t="s">
+        <v>326</v>
+      </c>
+      <c r="K13" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="L13" s="50" t="s">
+        <v>356</v>
+      </c>
+      <c r="M13" s="50" t="s">
+        <v>357</v>
+      </c>
+      <c r="N13" s="50" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="50" t="s">
+        <v>270</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>396</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="50" t="s">
+        <v>269</v>
+      </c>
+      <c r="F14" s="50" t="s">
+        <v>328</v>
+      </c>
+      <c r="G14" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="H14" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="I14" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="J14" s="50" t="s">
+        <v>333</v>
+      </c>
+      <c r="K14" s="50" t="s">
+        <v>334</v>
+      </c>
+      <c r="L14" s="50" t="s">
+        <v>354</v>
+      </c>
+      <c r="M14" s="50" t="s">
+        <v>355</v>
+      </c>
+      <c r="N14" s="50" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="50" t="s">
+        <v>271</v>
+      </c>
+      <c r="B15" s="50" t="s">
+        <v>397</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>233</v>
+      </c>
+      <c r="E15" s="50" t="s">
+        <v>269</v>
+      </c>
+      <c r="F15" s="50" t="s">
+        <v>272</v>
+      </c>
+      <c r="G15" s="50" t="s">
+        <v>331</v>
+      </c>
+      <c r="H15" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="I15" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="J15" s="50" t="s">
+        <v>407</v>
+      </c>
+      <c r="K15" s="50" t="s">
+        <v>273</v>
+      </c>
+      <c r="L15" s="50" t="s">
+        <v>352</v>
+      </c>
+      <c r="M15" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="N15" s="50" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="50" t="s">
+        <v>274</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>398</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>233</v>
+      </c>
+      <c r="E16" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="F16" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="G16" s="50" t="s">
+        <v>337</v>
+      </c>
+      <c r="H16" s="50" t="s">
+        <v>338</v>
+      </c>
+      <c r="I16" s="50" t="s">
+        <v>339</v>
+      </c>
+      <c r="J16" s="50" t="s">
         <v>340</v>
       </c>
-      <c r="D12" s="81" t="s">
-        <v>209</v>
-      </c>
-      <c r="E12" s="81" t="s">
+      <c r="K16" s="50" t="s">
         <v>341</v>
       </c>
-      <c r="F12" s="81" t="s">
+      <c r="L16" s="50" t="s">
+        <v>350</v>
+      </c>
+      <c r="M16" s="50" t="s">
+        <v>351</v>
+      </c>
+      <c r="N16" s="50" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="132" x14ac:dyDescent="0.35">
+      <c r="A17" s="50" t="s">
+        <v>275</v>
+      </c>
+      <c r="B17" s="50" t="s">
+        <v>399</v>
+      </c>
+      <c r="C17" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="50" t="s">
+        <v>409</v>
+      </c>
+      <c r="F17" s="50" t="s">
+        <v>411</v>
+      </c>
+      <c r="G17" s="50" t="s">
+        <v>414</v>
+      </c>
+      <c r="H17" s="50" t="s">
         <v>342</v>
       </c>
-      <c r="G12" s="81" t="s">
+      <c r="I17" s="50" t="s">
         <v>343</v>
       </c>
-      <c r="H12" s="81" t="s">
+      <c r="J17" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="K17" s="50" t="s">
+        <v>420</v>
+      </c>
+      <c r="L17" s="50" t="s">
+        <v>348</v>
+      </c>
+      <c r="M17" s="50" t="s">
+        <v>349</v>
+      </c>
+      <c r="N17" s="50" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>400</v>
+      </c>
+      <c r="C18" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>233</v>
+      </c>
+      <c r="E18" s="50" t="s">
+        <v>409</v>
+      </c>
+      <c r="F18" s="50" t="s">
+        <v>412</v>
+      </c>
+      <c r="G18" s="50" t="s">
+        <v>415</v>
+      </c>
+      <c r="H18" s="50" t="s">
         <v>344</v>
       </c>
-      <c r="I12" s="81" t="s">
+      <c r="I18" s="50" t="s">
         <v>345</v>
       </c>
-      <c r="J12" s="81" t="s">
-        <v>210</v>
-      </c>
-      <c r="K12" s="81" t="s">
-        <v>308</v>
-      </c>
-      <c r="L12" s="81" t="s">
+      <c r="J18" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="K18" s="50" t="s">
+        <v>421</v>
+      </c>
+      <c r="L18" s="50" t="s">
         <v>346</v>
       </c>
-      <c r="M12" s="81" t="s">
+      <c r="M18" s="50" t="s">
         <v>347</v>
       </c>
-      <c r="N12" s="81" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="115.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="82" t="s">
-        <v>285</v>
-      </c>
-      <c r="B13" s="82" t="s">
-        <v>286</v>
-      </c>
-      <c r="C13" s="83" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="82" t="s">
-        <v>238</v>
-      </c>
-      <c r="E13" s="82" t="s">
-        <v>287</v>
-      </c>
-      <c r="F13" s="82" t="s">
-        <v>350</v>
-      </c>
-      <c r="G13" s="82" t="s">
-        <v>351</v>
-      </c>
-      <c r="H13" s="82" t="s">
-        <v>352</v>
-      </c>
-      <c r="I13" s="82" t="s">
-        <v>353</v>
-      </c>
-      <c r="J13" s="82" t="s">
-        <v>354</v>
-      </c>
-      <c r="K13" s="82" t="s">
-        <v>355</v>
-      </c>
-      <c r="L13" s="82" t="s">
-        <v>393</v>
-      </c>
-      <c r="M13" s="82" t="s">
-        <v>394</v>
-      </c>
-      <c r="N13" s="82" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="115.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="82" t="s">
-        <v>288</v>
-      </c>
-      <c r="B14" s="82" t="s">
-        <v>289</v>
-      </c>
-      <c r="C14" s="83" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="82" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="82" t="s">
-        <v>287</v>
-      </c>
-      <c r="F14" s="82" t="s">
-        <v>356</v>
-      </c>
-      <c r="G14" s="82" t="s">
-        <v>357</v>
-      </c>
-      <c r="H14" s="82" t="s">
-        <v>358</v>
-      </c>
-      <c r="I14" s="82" t="s">
-        <v>360</v>
-      </c>
-      <c r="J14" s="82" t="s">
-        <v>361</v>
-      </c>
-      <c r="K14" s="82" t="s">
-        <v>362</v>
-      </c>
-      <c r="L14" s="82" t="s">
-        <v>391</v>
-      </c>
-      <c r="M14" s="82" t="s">
-        <v>392</v>
-      </c>
-      <c r="N14" s="82" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="115.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="82" t="s">
-        <v>290</v>
-      </c>
-      <c r="B15" s="82" t="s">
-        <v>291</v>
-      </c>
-      <c r="C15" s="83" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="82" t="s">
-        <v>248</v>
-      </c>
-      <c r="E15" s="82" t="s">
-        <v>287</v>
-      </c>
-      <c r="F15" s="82" t="s">
-        <v>292</v>
-      </c>
-      <c r="G15" s="82" t="s">
-        <v>359</v>
-      </c>
-      <c r="H15" s="82" t="s">
-        <v>358</v>
-      </c>
-      <c r="I15" s="82" t="s">
-        <v>363</v>
-      </c>
-      <c r="J15" s="82" t="s">
-        <v>364</v>
-      </c>
-      <c r="K15" s="82" t="s">
-        <v>293</v>
-      </c>
-      <c r="L15" s="82" t="s">
-        <v>389</v>
-      </c>
-      <c r="M15" s="82" t="s">
-        <v>390</v>
-      </c>
-      <c r="N15" s="82" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="115.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="82" t="s">
-        <v>294</v>
-      </c>
-      <c r="B16" s="82" t="s">
-        <v>295</v>
-      </c>
-      <c r="C16" s="83" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="82" t="s">
-        <v>248</v>
-      </c>
-      <c r="E16" s="82" t="s">
-        <v>211</v>
-      </c>
-      <c r="F16" s="82" t="s">
-        <v>365</v>
-      </c>
-      <c r="G16" s="82" t="s">
-        <v>366</v>
-      </c>
-      <c r="H16" s="82" t="s">
-        <v>367</v>
-      </c>
-      <c r="I16" s="82" t="s">
-        <v>368</v>
-      </c>
-      <c r="J16" s="82" t="s">
-        <v>369</v>
-      </c>
-      <c r="K16" s="82" t="s">
-        <v>370</v>
-      </c>
-      <c r="L16" s="82" t="s">
-        <v>387</v>
-      </c>
-      <c r="M16" s="82" t="s">
-        <v>388</v>
-      </c>
-      <c r="N16" s="82" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="132" x14ac:dyDescent="0.35">
-      <c r="A17" s="82" t="s">
-        <v>296</v>
-      </c>
-      <c r="B17" s="82" t="s">
-        <v>297</v>
-      </c>
-      <c r="C17" s="84" t="s">
+      <c r="N18" s="50" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="82.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="50" t="s">
+        <v>423</v>
+      </c>
+      <c r="B19" s="50" t="s">
+        <v>408</v>
+      </c>
+      <c r="C19" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="82" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="82" t="s">
-        <v>298</v>
-      </c>
-      <c r="F17" s="82" t="s">
-        <v>371</v>
-      </c>
-      <c r="G17" s="82" t="s">
-        <v>372</v>
-      </c>
-      <c r="H17" s="82" t="s">
-        <v>373</v>
-      </c>
-      <c r="I17" s="82" t="s">
-        <v>374</v>
-      </c>
-      <c r="J17" s="82" t="s">
-        <v>375</v>
-      </c>
-      <c r="K17" s="82" t="s">
-        <v>376</v>
-      </c>
-      <c r="L17" s="82" t="s">
-        <v>385</v>
-      </c>
-      <c r="M17" s="82" t="s">
-        <v>386</v>
-      </c>
-      <c r="N17" s="82" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="115.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="82" t="s">
-        <v>299</v>
-      </c>
-      <c r="B18" s="82" t="s">
-        <v>300</v>
-      </c>
-      <c r="C18" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="82" t="s">
-        <v>248</v>
-      </c>
-      <c r="E18" s="82" t="s">
-        <v>298</v>
-      </c>
-      <c r="F18" s="82" t="s">
-        <v>377</v>
-      </c>
-      <c r="G18" s="82" t="s">
-        <v>378</v>
-      </c>
-      <c r="H18" s="82" t="s">
-        <v>379</v>
-      </c>
-      <c r="I18" s="82" t="s">
-        <v>380</v>
-      </c>
-      <c r="J18" s="82" t="s">
-        <v>381</v>
-      </c>
-      <c r="K18" s="82" t="s">
-        <v>382</v>
-      </c>
-      <c r="L18" s="82" t="s">
-        <v>383</v>
-      </c>
-      <c r="M18" s="82" t="s">
-        <v>384</v>
-      </c>
-      <c r="N18" s="82" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="85"/>
-      <c r="B19" s="76"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
+      <c r="D19" s="95" t="s">
+        <v>227</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>409</v>
+      </c>
+      <c r="F19" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="G19" s="50" t="s">
+        <v>413</v>
+      </c>
+      <c r="H19" s="50" t="s">
+        <v>417</v>
+      </c>
+      <c r="I19" s="50" t="s">
+        <v>416</v>
+      </c>
+      <c r="J19" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="K19" s="50" t="s">
+        <v>418</v>
+      </c>
+      <c r="L19" s="50" t="s">
+        <v>346</v>
+      </c>
+      <c r="M19" s="50" t="s">
+        <v>422</v>
+      </c>
+      <c r="N19" s="50" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="85"/>
-      <c r="B20" s="76"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="76"/>
-      <c r="E20" s="76"/>
+      <c r="A20" s="53"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="85"/>
-      <c r="B21" s="76"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="76"/>
-      <c r="E21" s="76"/>
+      <c r="A21" s="53"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="85"/>
-      <c r="B22" s="76"/>
-      <c r="C22" s="85"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
+      <c r="A22" s="53"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="85"/>
-      <c r="B23" s="76"/>
-      <c r="C23" s="85"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
+      <c r="A23" s="53"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="85"/>
-      <c r="B24" s="76"/>
-      <c r="C24" s="85"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
+      <c r="A24" s="53"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="85"/>
-      <c r="B25" s="76"/>
-      <c r="C25" s="85"/>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
+      <c r="A25" s="53"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="85"/>
-      <c r="B26" s="76"/>
-      <c r="C26" s="85"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
+      <c r="A26" s="53"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="85"/>
-      <c r="B27" s="76"/>
-      <c r="C27" s="85"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
+      <c r="A27" s="53"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="85"/>
-      <c r="B28" s="76"/>
-      <c r="C28" s="85"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
+      <c r="A28" s="53"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="85"/>
-      <c r="B29" s="76"/>
-      <c r="C29" s="85"/>
-      <c r="D29" s="76"/>
-      <c r="E29" s="76"/>
+      <c r="A29" s="53"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="85"/>
-      <c r="B30" s="76"/>
-      <c r="C30" s="85"/>
-      <c r="D30" s="76"/>
-      <c r="E30" s="76"/>
+      <c r="A30" s="53"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="85"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="85"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="76"/>
+      <c r="A31" s="53"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="85"/>
-      <c r="B32" s="76"/>
-      <c r="C32" s="85"/>
-      <c r="D32" s="76"/>
-      <c r="E32" s="76"/>
+      <c r="A32" s="53"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="85"/>
-      <c r="B33" s="76"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
+      <c r="A33" s="53"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="85"/>
-      <c r="B34" s="76"/>
-      <c r="C34" s="85"/>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
+      <c r="A34" s="53"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="85"/>
-      <c r="B35" s="76"/>
-      <c r="C35" s="85"/>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
+      <c r="A35" s="53"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="53"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="85"/>
-      <c r="B36" s="76"/>
-      <c r="C36" s="85"/>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
+      <c r="A36" s="53"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="85"/>
-      <c r="B37" s="76"/>
-      <c r="C37" s="85"/>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
+      <c r="A37" s="53"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="85"/>
-      <c r="B38" s="76"/>
-      <c r="C38" s="85"/>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
+      <c r="A38" s="53"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="85"/>
-      <c r="B39" s="76"/>
-      <c r="C39" s="85"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
+      <c r="A39" s="53"/>
+      <c r="B39" s="46"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="85"/>
-      <c r="B40" s="76"/>
-      <c r="C40" s="85"/>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
+      <c r="A40" s="53"/>
+      <c r="B40" s="46"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="46"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="85"/>
-      <c r="B41" s="76"/>
-      <c r="C41" s="85"/>
-      <c r="D41" s="76"/>
-      <c r="E41" s="76"/>
+      <c r="A41" s="53"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="46"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="85"/>
-      <c r="B42" s="76"/>
-      <c r="C42" s="85"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
+      <c r="A42" s="53"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="53"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="46"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="85"/>
-      <c r="B43" s="76"/>
-      <c r="C43" s="85"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
+      <c r="A43" s="53"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="53"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="46"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="85"/>
-      <c r="B44" s="76"/>
-      <c r="C44" s="85"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
+      <c r="A44" s="53"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="85"/>
-      <c r="B45" s="76"/>
-      <c r="C45" s="85"/>
-      <c r="D45" s="76"/>
-      <c r="E45" s="76"/>
+      <c r="A45" s="53"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="85"/>
-      <c r="B46" s="76"/>
-      <c r="C46" s="85"/>
-      <c r="D46" s="76"/>
-      <c r="E46" s="76"/>
+      <c r="A46" s="53"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="85"/>
-      <c r="B47" s="76"/>
-      <c r="C47" s="85"/>
-      <c r="D47" s="76"/>
-      <c r="E47" s="76"/>
+      <c r="A47" s="53"/>
+      <c r="B47" s="46"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="85"/>
-      <c r="B48" s="76"/>
-      <c r="C48" s="85"/>
-      <c r="D48" s="76"/>
-      <c r="E48" s="76"/>
+      <c r="A48" s="53"/>
+      <c r="B48" s="46"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="85"/>
-      <c r="B49" s="76"/>
-      <c r="C49" s="85"/>
-      <c r="D49" s="76"/>
-      <c r="E49" s="76"/>
+      <c r="A49" s="53"/>
+      <c r="B49" s="46"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="1">
